--- a/Commons/InventoryWebApp/src/main/webapp/WEB-INF/Templates/预出库模板.xlsx
+++ b/Commons/InventoryWebApp/src/main/webapp/WEB-INF/Templates/预出库模板.xlsx
@@ -27,9 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>预入库</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+  <si>
+    <t>预出库</t>
   </si>
   <si>
     <t>区域</t>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>项目经理</t>
-  </si>
-  <si>
-    <t>预出库</t>
   </si>
   <si>
     <t>实出库</t>
@@ -1152,69 +1149,69 @@
         <v>7</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
